--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0091.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0091.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Celebration Gift</t>
+          <t>Món Quà Chúc Mừng</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dấu Chân ở Rinascita III</t>
+          <t>Dấu chân ở Rinascita III</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Exploration: Dimmr Plains</t>
+          <t>Thám hiểm: Đồng bằng Dimmr</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Số lượng không đủ</t>
+          <t>Số lượng không đủ.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Invisiblity</t>
+          <t>Tàng hình</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Flash</t>
+          <t>Tia Chớp</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Kiên Cường</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Sức chịu đựng</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mimic</t>
+          <t>Quái Giả Hình</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Nổ</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Restraint</t>
+          <t>Kiềm chế</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Last Stand</t>
+          <t>Trận Chiến Cuối Cùng</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Berserk</t>
+          <t>Cuồng Nộ</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Forestall</t>
+          <t>Ngăn Chặn</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Taunt</t>
+          <t>Khiêu khích</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Patience</t>
+          <t>Kiên nhẫn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Recharge</t>
+          <t>Nạp Năng Lượng</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Chuyển hóa</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Vòng tuần hoàn</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Flank Force</t>
+          <t>Lực Lượng Tấn Công Cạnh Sườn</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Superpower</t>
+          <t>Siêu Năng Lực</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Versatility</t>
+          <t>Đa năng</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Complete Hero's Rend II</t>
+          <t>Hoàn thành Bản Heroic II</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Ngọn Lửa Trong Tim"</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Flames of Heart"</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Bay Dưới Lòng Đất</t>
+          <t>Hoàn thành Thử Thách Bay Ngầm</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đánh bại Kerasaurs bị mắc kẹt trên Titanbone Expanse</t>
+          <t>Tiêu diệt bọn Kerasaur bị mắc kẹt trên Titanbone Expanse</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Đến Đồi Capitoline trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang"</t>
+          <t>Đến được Đồi Capitoline trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang".</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Thắng Bán Kết trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang"</t>
+          <t>Chiến thắng trận Bán Kết trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang"</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Đến Tháp Chuông trong Nhiệm Vụ Chính "Ngọn Lửa Trong Tim"</t>
+          <t>Đến Tháp Chuông trong nhiệm vụ chính "Lửa Trong Tim"</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Cách nhận: Đánh bại Lupa</t>
+          <t>Cách nhận: Defeat Lupa</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Cách nhận: Đánh bại Calcharo</t>
+          <t>Cách nhận: Defeat Calcharo</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Cách nhận: Đạt kỷ lục cao nhất 500 Fame Flags</t>
+          <t>Cách nhận: Đạt kỷ lục 500 Cờ Danh Vọng</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Cách nhận: Đạt kỷ lục cao nhất 1.000 Fame Flags</t>
+          <t>Cách nhận: Đạt kỷ lục 1.000 Cờ Danh Vọng</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Cách nhận: Đạt kỷ lục cao nhất 1.600 Fame Flags</t>
+          <t>Cách nhận: Đạt kỷ lục 1.600 Cờ Danh Vọng</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Thử Thách Bị Khóa</t>
+          <t>Thử Thách Đã Khóa</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Bạn đã rời Chế độ Hợp tác</t>
+          <t>Bạn đã thoát khỏi Chế độ Hợp tác</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Một thành viên trong nhóm đã rời thử thách</t>
+          <t>Một thành viên đã rời khỏi thử thách</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Đến Septimont trong Nhiệm vụ Chính "Bóng tối vinh quang"</t>
+          <t>Đến Septimont trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang"</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Đang hưng phấn</t>
+          <t>Bị Sương Mù Xâm Nhập</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Tôi đang chờ một ván bài hoàn hảo</t>
+          <t>Ta là "Đợi Tay Bài Hoàn Hảo"</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Luật chiến thắng đã được quyết định</t>
+          <t>Luật Chiến Thắng Đã Được Định Đoạt</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Giáo sư Echo</t>
+          <t>Chuyên Gia Tần Số</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Cứng nhất! Bất khả chiến bại! Vô đối!</t>
+          <t>Hùng Mạnh Nhất! Bất Khả Chiến Bại! Vô Địch!</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Bạn đã tích trữ đủ kho báu chưa?</t>
+          <t>Kho báu của ngươi còn đủ không?</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Echo Tamer</t>
+          <t>Người Thuần Hóa Tiếng Vọng</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Heart of the Cards, Guide Me</t>
+          <t>Trái Tim Quân Bài, Dẫn Lối Ta</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Difficult</t>
+          <t>Khó nhằn thật</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Hồi V "Bóng Tối Vinh Quang" để có trải nghiệm tốt hơn</t>
+          <t>Hoàn thành Chương II Cảnh V "Bóng Tối Vinh Quang" để trải nghiệm tốt hơn</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Vượt quá yêu cầu hiệu ứng Sonata</t>
+          <t>Đã vượt quá yêu cầu Hiệu ứng Sonata</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Prop</t>
+          <t>Vật phẩm</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Dream Box</t>
+          <t>Hộp Mộng</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Difficult</t>
+          <t>Khó nhằn thật</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Dreamland Coupons</t>
+          <t>Phiếu Giấc Mơ</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Frequency Crystal</t>
+          <t>Pha Lê Tần Số</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Daily Coupon</t>
+          <t>Phiếu thưởng hàng ngày</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai đoạn trước ở bất kỳ độ khó nào để mở khóa</t>
+          <t>Hoàn thành Giai Đoạn trước ở bất kỳ độ khó nào để mở khóa</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Blessing</t>
+          <t>Phước Lành</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Đánh bại Grandino Gladiator để mở khóa</t>
+          <t>Đánh bại Võ sĩ Grandino để mở khóa</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Đánh bại Grandino Agent để mở khóa</t>
+          <t>Đánh bại Đặc vụ Grandino để mở khóa</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đánh bại Grandino Head để mở khóa</t>
+          <t>Đánh bại Thủ lĩnh Grandino để mở khóa</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Đánh bại Raul the Dustbound để mở khóa</t>
+          <t>Đánh bại Raul the Dustbound để mở khóa.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Đánh bại Anxious Man để mở khóa</t>
+          <t>Đánh bại Người Đàn Ông Lo Âu để mở khóa.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Đánh bại Silent Elder để mở khóa</t>
+          <t>Đánh bại Trưởng Lão Câm Lặng để mở khóa</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Đánh bại Care-Refusing Patient để mở khóa</t>
+          <t>Đánh bại Bệnh Nhân Bướng Bỉnh để mở khóa</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Đánh bại Recovering Patient để mở khóa</t>
+          <t>Đánh bại Bệnh Nhân Đang Phục Hồi để mở khóa</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Đánh bại Gallus the Nightmare để mở khóa</t>
+          <t>Đánh bại Gallus Ác Mộng để mở khóa</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Đánh bại Cheerful Duelist để mở khóa</t>
+          <t>Đánh bại Kẻ Đấu Tay Đôi Vui Vẻ để mở khóa</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Đánh bại Angry Woman để mở khóa</t>
+          <t>Đánh bại Người Phụ Nữ Giận Dữ để mở khóa.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Đánh bại Gallus the Nightmare để mở khóa</t>
+          <t>Đánh bại Gallus Ác Mộng để mở khóa</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Đánh bại Furius the Firebrand để mở khóa</t>
+          <t>Tiêu diệt Furius the Firebrand để mở khóa</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Đánh bại Furius the Firebrand để mở khóa</t>
+          <t>Tiêu diệt Furius the Firebrand để mở khóa</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Đánh bại Contemplative Duelist để mở khóa</t>
+          <t>Tiêu diệt Kẻ Song Đấu Trầm Tĩnh để mở khóa</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Đánh bại Arrogant Duelist để mở khóa</t>
+          <t>Đánh bại Kẻ Khiêu Chiến Kiêu Ngạo để mở khóa.</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Đánh bại Raul the Dustbound để mở khóa</t>
+          <t>Đánh bại Raul the Dustbound để mở khóa.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Đang kích hoạt</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Bị Động</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,8 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Không thể sử dụng Blessing lúc này
-```</t>
+          <t>Không thể sử dụng Phúc Lành lúc này</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7995,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Bỏ qua</t>
+          <t>Bỏ Qua</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8065,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Batch Management</t>
+          <t>Quản Lý Hàng Loạt</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8135,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Batch Manage</t>
+          <t>Quản Lý Hàng Loạt</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8205,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Chưa chọn Echo</t>
+          <t>Chưa chọn Echo nào.</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8275,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Khóa</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8345,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Hủy Bỏ</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8485,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Undiscard</t>
+          <t>Bỏ Lại Đằng Sau</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8555,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Quản lý Echo</t>
+          <t>Quản Lý Tiếng Vọng</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8695,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Cài đặt Tự động Loại Bỏ</t>
+          <t>Cài Đặt Tự Động Loại Bỏ</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8765,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Empty Plan</t>
+          <t>Kế Hoạch Trống Rỗng</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8835,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Tên</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8975,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Tự động loại bỏ theo kế hoạch này</t>
+          <t>Loại bỏ theo kế hoạch này</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9045,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9115,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Chỉ Tìm Kiếm</t>
+          <t>Chỉ tìm kiếm</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9185,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Save Plan</t>
+          <t>Lưu Kế Hoạch</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9255,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Vui lòng chọn ít nhất một bộ lọc</t>
+          <t>Hãy chọn ít nhất một bộ lọc</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9325,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Chỉnh sửa</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9395,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9465,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9535,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Save Only</t>
+          <t>Chỉ Lưu</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9605,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Xem (Tự Động Loại Bỏ)</t>
+          <t>Xem (Tự động loại bỏ)</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9675,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Xem (Tự Động Khóa)</t>
+          <t>Xem (Tự động khóa)</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9815,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10025,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Đã loại bỏ hàng loạt</t>
+          <t>Đã bỏ hàng loạt</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10095,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Đã hoàn tác loại bỏ hàng loạt</t>
+          <t>Đã hoàn tác bỏ hàng loạt</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10165,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Kế hoạch đã kích hoạt</t>
+          <t>Kế Hoạch đã kích hoạt</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10235,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Kế hoạch đã vô hiệu hóa</t>
+          <t>Kế Hoạch đã tắt</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10305,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kế hoạch đã lưu</t>
+          <t>Kế Hoạch đã lưu</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10375,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tự động loại bỏ Echo không phải 5 sao đã bật</t>
+          <t>Đã bật Tự Động Loại Bỏ Echo Không Phải 5 Sao</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10445,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Auto-Discard Non-5-Star Echoes</t>
+          <t>Tự Động Loại Bỏ Echo Không Phải 5 Sao</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10515,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Đặt lại Modes</t>
+          <t>Chế độ Đặt lại</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10585,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Disable Only</t>
+          <t>Chỉ Vô Hiệu Hóa</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10655,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Xóa kế hoạch và vô hiệu hóa</t>
+          <t>Hoàn thành Kế Hoạch và Vô Hiệu Hóa</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10795,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Plan Đặt lại</t>
+          <t>Đặt lại Kế Hoạch</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10865,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Kế hoạch đã vô hiệu hóa</t>
+          <t>Kế Hoạch đã tắt</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10935,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Disable</t>
+          <t>Vô Hiệu Hóa</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11075,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Exit Anyway</t>
+          <t>Thoát Khỏi Dù Sao</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11145,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Exit Confirmation</t>
+          <t>Xác Nhận Thoát</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11215,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Kích hoạt kế hoạch khi lưu</t>
+          <t>Lưu Kế Hoạch Khi Lưu Trữ</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11285,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Loại Echo này sẽ được tự động khóa</t>
+          <t>Loại Tổ Tacet này sẽ được khóa tự động.</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11355,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Loại Echo này sẽ được tự động loại bỏ</t>
+          <t>Loại Tổ Tacet này sẽ bị loại bỏ tự động.</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11425,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Tự động loại bỏ cho loại Echo này đã bị vô hiệu hóa và thay thế bằng Tự động khóa</t>
+          <t>Tính năng tự động loại bỏ cho loại Echo này đã bị vô hiệu hóa và thay bằng tự động khóa</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11495,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tự động khóa cho loại Echo này đã bị vô hiệu hóa và thay thế bằng Tự động loại bỏ</t>
+          <t>Tính năng tự động khóa cho loại Echo này đã bị vô hiệu hóa và thay bằng tự động loại bỏ</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11565,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Edit Plan</t>
+          <t>Chỉnh sửa kế hoạch</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11705,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Đặt lại Plan</t>
+          <t>Đặt lại Kế Hoạch</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11915,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Lưu kế hoạch thành công</t>
+          <t>Kế hoạch đã lưu thành công</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11985,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Lưu và kích hoạt kế hoạch thành công</t>
+          <t>Lưu và kích hoạt Kế Hoạch thành công</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12055,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Enabled</t>
+          <t>Đã bật</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12125,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Không có Echo để xử lý</t>
+          <t>Không có Echo nào để xử lý.</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12195,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Đã hoàn tất xử lý hàng loạt cho Echo sở hữu</t>
+          <t>Đã xử lý hàng loạt cho Echo sở hữu</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12265,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Manage Owned Echoes</t>
+          <t>Quản Lý Echo Đã Sở Hữu</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12335,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Share Anyway</t>
+          <t>Chia sẻ ngay</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12475,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Share Confirmation</t>
+          <t>Xác nhận chia sẻ</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12545,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Nhập Mã Kế Hoạch tại đây</t>
+          <t>Nhập Mã Kế hoạch tại đây</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12685,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Nhập kế hoạch thành công</t>
+          <t>Nhập Kế Hoạch thành công</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12755,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Định dạng Mã Kế Hoạch không hợp lệ</t>
+          <t>Định dạng Mã Kế hoạch không hợp lệ</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12825,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Đang Đọc</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12895,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>My Plan Code</t>
+          <t>Mã Kế Hoạch Của Ta</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12965,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13035,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Chia sẻ</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13105,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Import Plans</t>
+          <t>Nhập Kế Hoạch</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13175,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Đọc Mã Kế hoạch</t>
+          <t>Đọc Mã Kế Hoạch</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13245,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Mã Kế Hoạch đã được cập nhật phiên bản mới nhất</t>
+          <t>Mã Kế Hoạch đã cập nhật phiên bản mới nhất</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13315,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Sao chép Mã Kế Hoạch vào bộ nhớ tạm</t>
+          <t>Mã Kế Hoạch đã sao chép vào bộ nhớ tạm</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13455,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Kế hoạch đã được kích hoạt</t>
+          <t>Kế Hoạch đã bật</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13525,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Enable Plan</t>
+          <t>Kích Hoạt Kế Hoạch</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13595,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bạn đang sử dụng kế hoạch đề xuất</t>
+          <t>Ngươi đang dùng kế hoạch đề xuất rồi mà.</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13665,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Áp dụng kế hoạch mới cho Echo sở hữu</t>
+          <t>Áp dụng kế hoạch mới cho các Echo đã sở hữu</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13945,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14295,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Lỗi xác thực loại COST</t>
+          <t>LỖI KIỂM TRA LOẠI CHI PHÍ</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14365,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Không có kế hoạch quản lý đang sử dụng</t>
+          <t>Chưa có kế hoạch quản lý nào được áp dụng</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14435,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Đọc thất bại bộ Sonata</t>
+          <t>Đọc bộ Sonata thất bại</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14505,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Quản lý Echo chưa khả dụng</t>
+          <t>Chức Năng Quản Lý Tiếng Vọng Chưa Được Mở Khóa</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14575,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Kế hoạch Điều Chỉnh (Echo 2 sao không thể điều chỉnh, chỉ có thể nâng cấp)</t>
+          <t>Kế Hoạch Điều Chỉnh (Echo 2 sao không thể điều chỉnh, chỉ có thể nâng cấp)</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14645,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Enable Sync Tuning</t>
+          <t>Bật Đồng Bộ Hóa Âm Thanh</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14715,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Disable Sync Tuning</t>
+          <t>Vô Hiệu Hóa Đồng Bộ Tần Số</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14785,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Nâng cấp &amp; Điều Chỉnh</t>
+          <t>Nâng cấp &amp; Điều chỉnh</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14855,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Tune Tất cả</t>
+          <t>Điệu nhạc toàn bộ</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14925,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Chuẩn bị Điều Chỉnh</t>
+          <t>Để được Điều Chỉnh</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14995,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Không thể xem chi tiết Resonator thử nghiệm</t>
+          <t>Không thể kiểm tra thông tin Resonator Thử Nghiệm</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15065,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Basic Gradation Dream Box</t>
+          <t>Hộp Mộng Cơ Bản</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15135,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Medium Gradation Dream Box</t>
+          <t>Hộp Mộng Phân Cấp Cấp Trung</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15205,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Advanced Gradation Dream Box</t>
+          <t>Hộp Mộng Ước Phân Cấp Cao Cấp</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15275,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Premium Gradation Dream Box</t>
+          <t>Hộp Mộng Ước Phân Cấp Cao Cấp</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15345,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Basic Devouring Dream Box</t>
+          <t>Hộp Giấc Mơ Nuốt Chửng Cơ Bản</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15415,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Medium Devouring Dream Box</t>
+          <t>Hộp Giấc Mơ Nuốt Chửng Cỡ Trung</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15485,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Advanced Devouring Dream Box</t>
+          <t>Hộp Giấc Mơ Nuốt Chửng Tiến Hóa</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15555,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Premium Devouring Dream Box</t>
+          <t>Hộp Giấc Mơ Nuốt Chửng Cao Cấp</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15625,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Basic Exchange Dream Box</t>
+          <t>Hộp Mộng Ước Đổi Cơ bản</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15695,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Medium Exchange Dream Box</t>
+          <t>Hộp Mộng Giao Dịch Cấp Trung</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15765,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Advanced Exchange Dream Box</t>
+          <t>Hộp Mộng Ước Trao Đổi Cao Cấp</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15835,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Premium Exchange Dream Box</t>
+          <t>Hộp Mộng Ước Trao Đổi Cao Cấp</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15905,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Basic Dream Integration Box</t>
+          <t>Hộp Hòa Nhập Giấc Mơ Cơ Bản</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15975,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Medium Dream Integration Box</t>
+          <t>Hộp Hòa Nhập Giấc Mộng Cỡ Trung</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16045,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Advanced Dream Integration Box</t>
+          <t>Hộp Hòa Nhập Giấc Mơ Tiến Hóa</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16115,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Premium Dream Integration Box</t>
+          <t>Hộp Hòa Nhập Giấc Mơ Cao Cấp</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16185,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Dream Contagion</t>
+          <t>Lây Nhiễm Mộng</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16255,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hero's Slash</t>
+          <t>Thái Anh Hùng</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16535,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Đánh bại Người Đàn Ông Phấn Khích để mở khóa</t>
+          <t>Hạ gục Người Đàn Ông Phấn Khích để mở khóa</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16605,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Mua</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16675,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Bán</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16745,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Dismiss</t>
+          <t>Bỏ qua</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16815,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16885,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Free Refresh</t>
+          <t>Làm Mới Miễn Phí</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17025,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Enter Dreamland</t>
+          <t>Đặt chân vào Xứ Sở Mộng Mơ</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17095,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17165,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Collections</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17235,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17445,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hide</t>
+          <t>Ẩn</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17515,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Unhide</t>
+          <t>Hiện Lại</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17585,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Daily Coupon +1</t>
+          <t>Phiếu thưởng hàng ngày +1</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17655,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Devour Immunity</t>
+          <t>Miễn nhiễm Nuốt chửng</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17725,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Daily Coupon +3</t>
+          <t>Phiếu thưởng hàng ngày +3</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17795,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Daily Coupon +2</t>
+          <t>Phiếu thưởng hàng ngày +2</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17865,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Daily Coupon +4</t>
+          <t>Phiếu thưởng hàng ngày +4</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17935,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Daily Coupon +5</t>
+          <t>Phiếu thưởng hàng ngày +5</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18005,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>Đã mua</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18075,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Mua thất bại, thiếu Tinh Thể Tần Số</t>
+          <t>Mua thất bại, không đủ Tinh Thể Tần Số.</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18145,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>The The Nevermore</t>
+          <t>Nevermore</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18215,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Sonance Casket: Septimont</t>
+          <t>Hòm Thanh Âm: Septimont</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18495,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Được đề xuất</t>
+          <t>Đề xuất</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18775,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18845,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Where Lone Wolf Resides</t>
+          <t>Nơi Sói Cô Đơn Trú Ngụ</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18915,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Mở khóa qua Nhiệm Vụ Chính "Những Kẻ Bắt Giấc Mơ Trong Khu Vườn Bí Mật"</t>
+          <t>Mở khóa qua Nhiệm Vụ Chính "Những Giấc Mơ Trong Khu Vườn Bí Mật"</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18985,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Giai đoạn tiếp theo</t>
+          <t>Giai Đoạn Tiếp Theo</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19055,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Insufficient Frequency Crystals</t>
+          <t>Pha lê Tần số không đủ</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19125,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Shield Counter</t>
+          <t>Phản Khiên</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19195,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Stacking Liberation</t>
+          <t>Giải Phóng Tầng Chồng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19265,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Slow Time</t>
+          <t>Làm Chậm Thời Gian</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19335,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Fireball</t>
+          <t>Quả Cầu Lửa</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19405,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Xoáy Lốc</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19475,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Attack Speed</t>
+          <t>Tốc Độ Tấn Công</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19545,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19615,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19685,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19825,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Symphony of Beyond</t>
+          <t>Giao Hưởng Vượt Giới</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20175,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Phrolova's Music Sheet</t>
+          <t>Bản nhạc của Phrolova</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20245,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Phrolova's Violin</t>
+          <t>Đàn vĩ cầm của Phrolova</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20315,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Retained Concert Ticket</t>
+          <t>Vé Hoà Nhạc Đã Lưu</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20385,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Song of Red and Black</t>
+          <t>Khúc hát Đỏ và Đen</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20455,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Hidden Lycoris</t>
+          <t>Lycoris Ẩn Giấu</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20525,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Treading Through Woes</t>
+          <t>Vượt Qua Nỗi Đau</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20595,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>The Perfect Gap</t>
+          <t>Khoảng Lặng Hoàn Hảo</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20665,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Afterlife and Beyond</t>
+          <t>Hậu Thế Và Viễn Cảnh</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -26195,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Border Mountains</t>
+          <t>Núi Biên Giới</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26265,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Dreamborne: Kelpie</t>
+          <t>Dreamborne: Ngựa Nước Kelpie</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26335,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Dreamborne: Cuddle Wuddle</t>
+          <t>Dreamborne: Ôm Ấp Ấm Cúng</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26405,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Dreamborne: Lottie Lost</t>
+          <t>Dreamborne: Lottie Lạc Lối</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26475,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Dreamborne: Dragon of Dirge</t>
+          <t>Dreamborne: Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26545,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Dreamborne: Lightcrusher</t>
+          <t>Dreamborne: Nghiền Ánh Sáng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26615,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Dreamborne: Kerasaur</t>
+          <t>Dreamborne: Thằn Lằn Giày Kerasaur</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26685,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Dreamborne: Roseshroom</t>
+          <t>Dreamborne: Nấm Hồng Roseshroom</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26755,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Dreamborne: Baby Roseshroom</t>
+          <t>Giấc Mơ: Baby Roseshroom</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26825,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Dreamborne: Chop Chop</t>
+          <t>Giấc Mơ: Chop Chop</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26895,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Dreamborne: Crownless</t>
+          <t>Giấc Mơ: Crownless</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26965,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Dreamborne: Rage Against the Statue</t>
+          <t>Dreamborne: Nổi Giận Với Tượng</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27105,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27175,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Điểm Ảo ảnh Nhận được khi Hoàn thành</t>
+          <t>Điểm Ảo Ảnh Nhận Khi Hoàn Thành</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27245,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Điểm Ảo ảnh Nhận được trong Vùng Ký ức Phụ</t>
+          <t>Điểm Ảo Ảnh Nhận Được Trong Vùng Ký Ức Phụ</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27315,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Tổng Điểm Ảo ảnh Nhận được</t>
+          <t>Tổng Điểm Ảo Ảnh Nhận Được</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27455,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Dreamland Echoes</t>
+          <t>Tiếng Vọng Giấc Mơ</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27525,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Dreamland Prop</t>
+          <t>Đạo Cụ Giấc Mơ</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27595,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Dream Block</t>
+          <t>Khối Giấc Mơ</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27665,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn Hành động Hằng ngày</t>
+          <t>Đã đạt giới hạn hoạt động hàng ngày</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27735,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Acquired</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27805,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Chưa Nhận Được</t>
+          <t>Chưa nhận được</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27875,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Nhận tất cả</t>
+          <t>Nhận Tất Cả</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27945,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Tính năng này bị vô hiệu hóa trong Chế độ Đồng đội</t>
+          <t>Tính năng này bị vô hiệu hóa trong Chế độ Đồng đội.</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28015,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Dưới Sự Dẫn dắt của Kẻ thù</t>
+          <t>Dẫn Đầu Kẻ Thù</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28085,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>An Unexpected Soulmate</t>
+          <t>Một Tri Kỷ Bất Ngờ</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28155,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>The Dark Days Are Over</t>
+          <t>Những Ngày Tăm Tối Đã Kết Thúc</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28295,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Con đường đăng quang</t>
+          <t>Con Đường Lên Ngôi</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28365,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Nàng trở thành đôi mắt của ngươi, và ngươi là lưỡi kiếm của nàng</t>
+          <t>Con bé là đôi mắt của ngươi, còn ngươi là lưỡi kiếm của nó.</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28435,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Hunt Begins</t>
+          <t>Cuộc săn bắt đầu</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28505,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>As Foretold</t>
+          <t>Như Lời Tiên Tri</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28575,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Mặt Trời và Mặt Trăng</t>
+          <t>Thái Dương và Nguyệt Minh</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28645,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Đi theo Ánh sáng</t>
+          <t>Đi theo Ánh Sáng</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28715,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>The Heroes</t>
+          <t>Những Anh Hùng</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28785,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Where Sun Burns Brightest</t>
+          <t>Nơi Mặt Trời Cháy Sáng Nhất</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28855,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Cô đơn Ánh bạc nhạt nhòa</t>
+          <t>Cô Đơn Ánh Bạc Nhạt</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28925,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thiên tài là một lời nguyền</t>
+          <t>Thiên Tài Là Một Lời Nguyền</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28995,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Singular Answer</t>
+          <t>Câu Trả Lời Duy Nhất</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29065,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Dreamcatcher tại Khu Vườn Bí Mật</t>
+          <t>Những Kẻ Bắt Giấc Mơ Trong Vườn Bí Mật</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29135,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Gỉ sét, Kiếm và Mặt trời</t>
+          <t>Gỉ Sét, Kiếm và Mặt Trời</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29205,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Bằng Bàn Tay Cháy Bỏng Của Mặt Trời</t>
+          <t>Bởi Bàn Tay Rực Cháy của Mặt Trời</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29415,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29625,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Những Kẻ Mộng Mơ Trong Khu Vườn Bí Mật</t>
+          <t>Chương II: Rinascita - Những Thợ Bắt Giấc Mơ Trong Vườn Bí Mật</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29695,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Gỉ Sét, Kiếm và Mặt Trời</t>
+          <t>Chương II Rinascita: Gỉ Sét, Kiếm và Mặt Trời</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29765,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Dưới Bàn Tay Rực Cháy Của Mặt Trời</t>
+          <t>Chương II: By Sun's Burning Hand</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29835,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Rinascita Chương II: Dưới Ánh Trăng Định Mệnh</t>
+          <t>Chương II: Rinascita - Dưới Ánh Trăng Định Mệnh</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29905,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30045,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Hồi tưởng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30115,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Chi Phí</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30255,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Prepare</t>
+          <t>Chuẩn bị</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30325,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Cửa Hàng KU-Money</t>
+          <t>Cửa hàng KU-Money</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30395,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Matrix Durability</t>
+          <t>Độ Bền Ma Trận</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30465,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>TD Waves Bị Ngăn Chặn</t>
+          <t>Đã ngăn chặn làn sóng Tacet</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30535,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Combat Machines</t>
+          <t>Máy Chiến Đấu</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30605,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>KU-Roro's Weapons</t>
+          <t>Vũ khí của KU-Roro</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30745,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>KU-Roro's Weapons</t>
+          <t>Vũ khí của KU-Roro</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30815,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Ceiling</t>
+          <t>Trần Nhà</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30885,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Tường</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30955,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Mặt đất</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31095,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Tùy Chọn</t>
+          <t>Chọn Mô-đun tùy chọn</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31165,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Tactic Set Progress</t>
+          <t>Tiến Độ Bộ Chiến Thuật</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31235,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Tactics Overview</t>
+          <t>Tổng Quan Chiến Thuật</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31305,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31375,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Chiến Thuật Purple sẽ được thêm vào Bộ Chiến Thuật của bạn</t>
+          <t>Chiến Thuật Tím sẽ được thêm vào Bộ Chiến Thuật của cậu</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31445,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Chiến Thuật Gold sẽ được thêm vào Bộ Chiến Thuật của bạn</t>
+          <t>Chiến Thuật Vàng sẽ được thêm vào Bộ Chiến Thuật của bạn</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31515,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>TD Types</t>
+          <t>Loại Tacet</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31585,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Waves</t>
+          <t>Làn Sóng</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31725,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Insufficient Sim Creditss</t>
+          <t>Không đủ Tín Dụng Sim</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -32005,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Lone Bridge</t>
+          <t>Cây Cầu Cô Đơn</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32075,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Forsaken Court</t>
+          <t>Tòa Án Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32145,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Crumbling City</t>
+          <t>Thành Phố Đổ Nát</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32215,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Abyssal Pass</t>
+          <t>Lối Đi Vực Sâu</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32285,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Mazed Aisle</t>
+          <t>Lối Rối Loạn</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32355,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Sunken Ruins</t>
+          <t>Tàn Tích Chìm</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32425,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Lone Bridge</t>
+          <t>Cây Cầu Cô Đơn</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32495,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Forsaken Court</t>
+          <t>Tòa Án Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32565,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Crumbling City</t>
+          <t>Thành Phố Đổ Nát</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32635,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Abyssal Pass</t>
+          <t>Lối Đi Vực Sâu</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32705,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Mazed Aisle</t>
+          <t>Lối Rối Loạn</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32775,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Sunken Ruins</t>
+          <t>Tàn Tích Chìm</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32845,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Abyssal Pass</t>
+          <t>Lối Đi Vực Sâu</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32915,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Sunken Ruins</t>
+          <t>Tàn Tích Chìm</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32985,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Combat Drill</t>
+          <t>Bài Tập Chiến Đấu</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33055,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Synergy Drill</t>
+          <t>Huấn Luyện Cộng Hưởng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33125,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Total Defense Test</t>
+          <t>Kiểm tra Phòng Ngự Tổng</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33195,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Threat: Common</t>
+          <t>Mối Đe Dọa: Thông Thường</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33265,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Threat: Elite</t>
+          <t>Mối đe dọa: Tinh nhuệ</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Threat: Overlord</t>
+          <t>Mối đe dọa: Chúa tể</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33405,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Simulation Info</t>
+          <t>Thông Tin Mô Phỏng</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33475,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Sim Ingot</t>
+          <t>Thỏi Sim</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33545,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Combat Machines</t>
+          <t>Máy Chiến Đấu</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33615,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tactic Set</t>
+          <t>Bộ Chiến Thuật</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33685,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Save Available</t>
+          <t>Đã Lưu</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33755,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Không Available Tactics</t>
+          <t>Không có Chiến Thuật nào khả dụng</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33825,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mở khóa</t>
+          <t>Chưa đáp ứng đủ yêu cầu mở khóa</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33895,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Kỷ lục cao nhất</t>
+          <t>Kỷ Lục Cao Nhất</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33965,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Sim Ingot Obtained</t>
+          <t>Nhận được Thỏi Sim</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34035,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Combat Machine Unlocked</t>
+          <t>Máy Chiến Đấu Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34105,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Tactic Set Unlocked</t>
+          <t>Bộ Chiến Thuật Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34175,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Basic Mô-đun</t>
+          <t>Mô-đun Cơ Bản</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34245,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Optional Mô-đun I</t>
+          <t>Mô-đun Tùy Chọn I</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34315,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Optional Mô-đun II</t>
+          <t>Mô-đun Tùy Chọn II</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34385,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Combat Machine Upgraded</t>
+          <t>Máy Chiến Đấu Đã Nâng Cấp</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34525,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Triển khai Cost</t>
+          <t>Chi phí triển khai</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34595,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Không thể gỡ bỏ máy này</t>
+          <t>Không thể tháo máy này ra được</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34665,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Không Traits</t>
+          <t>Không có Thuộc tính</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34735,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Kiên Cường</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34805,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Velocity</t>
+          <t>Vận Tốc</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34875,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Deathsound</t>
+          <t>Âm Tử</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34945,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35015,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Tổ Tacet</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35085,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Wrath</t>
+          <t>Thịnh Nộ</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35155,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Bị Động</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35225,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Deathsound - Healing</t>
+          <t>Âm Tử - Hồi Phục</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35295,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Deathsound - Summon</t>
+          <t>Âm Tử - Triệu Hồi</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35365,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Deathsound - Contamination</t>
+          <t>Âm Tử - Ô Nhiễm</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35435,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Domain - Acceleration</t>
+          <t>Tổ Tacet - Tăng Tốc</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35505,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Domain - Shelter</t>
+          <t>Tổ Tacet - Nơi Trú Ẩn</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
